--- a/01_data/01_input_data/02_processed/01_paper_IAEE/inputs_IAEE_2025_run_2035_SP.xlsx
+++ b/01_data/01_input_data/02_processed/01_paper_IAEE/inputs_IAEE_2025_run_2035_SP.xlsx
@@ -36676,7 +36676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C361"/>
+  <dimension ref="A1:C349"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38129,10 +38129,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr"/>
+          <t>USA_Prod</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>10114848.63670832</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -38142,10 +38144,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Tunisia</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr"/>
+          <t>CM_Prod</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>2206445.191086497</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -38155,10 +38159,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Libya</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr"/>
+          <t>SA_Prod</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>1338762.310771848</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -38168,11 +38174,11 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>USA_Prod</t>
+          <t>TT_Prod</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>10114848.63670832</v>
+        <v>244187.5310400494</v>
       </c>
     </row>
     <row r="101">
@@ -38183,11 +38189,11 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>CM_Prod</t>
+          <t>ME_Prod</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>2206445.191086497</v>
+        <v>5194976.912176006</v>
       </c>
     </row>
     <row r="102">
@@ -38198,11 +38204,11 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>SA_Prod</t>
+          <t>QA_Prod</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>1338762.310771848</v>
+        <v>1768141.250753962</v>
       </c>
     </row>
     <row r="103">
@@ -38213,11 +38219,11 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>TT_Prod</t>
+          <t>AF_Prod</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>244187.5310400494</v>
+        <v>750869.2287163949</v>
       </c>
     </row>
     <row r="104">
@@ -38228,11 +38234,11 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>ME_Prod</t>
+          <t>MA_Prod</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>5194976.912176006</v>
+        <v>683.9000000000001</v>
       </c>
     </row>
     <row r="105">
@@ -38243,11 +38249,11 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>QA_Prod</t>
+          <t>AU_Prod</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>1768141.250753962</v>
+        <v>1482501.88823942</v>
       </c>
     </row>
     <row r="106">
@@ -38258,11 +38264,11 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>AF_Prod</t>
+          <t>CN_Prod</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>750869.2287163949</v>
+        <v>2288704.156833825</v>
       </c>
     </row>
     <row r="107">
@@ -38273,11 +38279,11 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>MA_Prod</t>
+          <t>JS_Prod</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>683.9000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108">
@@ -38288,11 +38294,11 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>AU_Prod</t>
+          <t>IN_Prod</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>1482501.88823942</v>
+        <v>308590.2229916077</v>
       </c>
     </row>
     <row r="109">
@@ -38303,11 +38309,11 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>CN_Prod</t>
+          <t>AS_Prod</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>2288704.156833825</v>
+        <v>1259517.180291699</v>
       </c>
     </row>
     <row r="110">
@@ -38318,11 +38324,11 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>JS_Prod</t>
+          <t>CR_Prod</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>0</v>
+        <v>1828659.302226193</v>
       </c>
     </row>
     <row r="111">
@@ -38333,11 +38339,11 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>IN_Prod</t>
+          <t>EG_Prod</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>308590.2229916077</v>
+        <v>557871.0357303467</v>
       </c>
     </row>
     <row r="112">
@@ -38348,11 +38354,11 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>AS_Prod</t>
+          <t>IM_Prod</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>1259517.180291699</v>
+        <v>1419953.943201544</v>
       </c>
     </row>
     <row r="113">
@@ -38363,11 +38369,11 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>CR_Prod</t>
+          <t>SE_Prod</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>1828659.302226193</v>
+        <v>0</v>
       </c>
     </row>
     <row r="114">
@@ -38378,11 +38384,11 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>EG_Prod</t>
+          <t>BE_LNG_exp</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>557871.0357303467</v>
+        <v>0</v>
       </c>
     </row>
     <row r="115">
@@ -38393,11 +38399,11 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>IM_Prod</t>
+          <t>HR_LNG_exp</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>1419953.943201544</v>
+        <v>0</v>
       </c>
     </row>
     <row r="116">
@@ -38408,7 +38414,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>SE_Prod</t>
+          <t>EE_LNG_exp</t>
         </is>
       </c>
       <c r="C116" t="n">
@@ -38423,7 +38429,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>nan_Prod</t>
+          <t>FI_LNG_exp</t>
         </is>
       </c>
       <c r="C117" t="n">
@@ -38438,7 +38444,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Tunisia_Prod</t>
+          <t>FR_LNG_exp</t>
         </is>
       </c>
       <c r="C118" t="n">
@@ -38453,7 +38459,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Libya_Prod</t>
+          <t>DE_LNG_exp</t>
         </is>
       </c>
       <c r="C119" t="n">
@@ -38468,7 +38474,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>BE_LNG_exp</t>
+          <t>EL_LNG_exp</t>
         </is>
       </c>
       <c r="C120" t="n">
@@ -38483,7 +38489,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>HR_LNG_exp</t>
+          <t>IE_LNG_exp</t>
         </is>
       </c>
       <c r="C121" t="n">
@@ -38498,7 +38504,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>EE_LNG_exp</t>
+          <t>IT_LNG_exp</t>
         </is>
       </c>
       <c r="C122" t="n">
@@ -38513,7 +38519,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>FI_LNG_exp</t>
+          <t>LV_LNG_exp</t>
         </is>
       </c>
       <c r="C123" t="n">
@@ -38528,7 +38534,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>FR_LNG_exp</t>
+          <t>LT_LNG_exp</t>
         </is>
       </c>
       <c r="C124" t="n">
@@ -38543,7 +38549,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>DE_LNG_exp</t>
+          <t>NL_LNG_exp</t>
         </is>
       </c>
       <c r="C125" t="n">
@@ -38558,7 +38564,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>EL_LNG_exp</t>
+          <t>PL_LNG_exp</t>
         </is>
       </c>
       <c r="C126" t="n">
@@ -38573,7 +38579,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>IE_LNG_exp</t>
+          <t>PT_LNG_exp</t>
         </is>
       </c>
       <c r="C127" t="n">
@@ -38588,7 +38594,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>IT_LNG_exp</t>
+          <t>ES_LNG_exp</t>
         </is>
       </c>
       <c r="C128" t="n">
@@ -38603,7 +38609,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>LV_LNG_exp</t>
+          <t>TR_LNG_exp</t>
         </is>
       </c>
       <c r="C129" t="n">
@@ -38618,7 +38624,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>LT_LNG_exp</t>
+          <t>UK_LNG_exp</t>
         </is>
       </c>
       <c r="C130" t="n">
@@ -38633,7 +38639,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>NL_LNG_exp</t>
+          <t>USA_LNG_exp</t>
         </is>
       </c>
       <c r="C131" t="n">
@@ -38648,7 +38654,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>PL_LNG_exp</t>
+          <t>SA_LNG_exp</t>
         </is>
       </c>
       <c r="C132" t="n">
@@ -38663,7 +38669,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>PT_LNG_exp</t>
+          <t>TT_LNG_exp</t>
         </is>
       </c>
       <c r="C133" t="n">
@@ -38678,7 +38684,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>ES_LNG_exp</t>
+          <t>ME_LNG_exp</t>
         </is>
       </c>
       <c r="C134" t="n">
@@ -38693,7 +38699,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>TR_LNG_exp</t>
+          <t>QA_LNG_exp</t>
         </is>
       </c>
       <c r="C135" t="n">
@@ -38708,7 +38714,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>UK_LNG_exp</t>
+          <t>AF_LNG_exp</t>
         </is>
       </c>
       <c r="C136" t="n">
@@ -38723,7 +38729,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>USA_LNG_exp</t>
+          <t>AU_LNG_exp</t>
         </is>
       </c>
       <c r="C137" t="n">
@@ -38738,7 +38744,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>SA_LNG_exp</t>
+          <t>CN_LNG_exp</t>
         </is>
       </c>
       <c r="C138" t="n">
@@ -38753,7 +38759,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>TT_LNG_exp</t>
+          <t>JS_LNG_exp</t>
         </is>
       </c>
       <c r="C139" t="n">
@@ -38768,7 +38774,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>ME_LNG_exp</t>
+          <t>IN_LNG_exp</t>
         </is>
       </c>
       <c r="C140" t="n">
@@ -38783,7 +38789,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>QA_LNG_exp</t>
+          <t>AS_LNG_exp</t>
         </is>
       </c>
       <c r="C141" t="n">
@@ -38798,7 +38804,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>AF_LNG_exp</t>
+          <t>RU_LNG_exp</t>
         </is>
       </c>
       <c r="C142" t="n">
@@ -38813,7 +38819,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>AU_LNG_exp</t>
+          <t>EG_LNG_exp</t>
         </is>
       </c>
       <c r="C143" t="n">
@@ -38828,7 +38834,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>CN_LNG_exp</t>
+          <t>IM_LNG_exp</t>
         </is>
       </c>
       <c r="C144" t="n">
@@ -38843,7 +38849,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>JS_LNG_exp</t>
+          <t>BE_LNG_imp</t>
         </is>
       </c>
       <c r="C145" t="n">
@@ -38858,7 +38864,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>IN_LNG_exp</t>
+          <t>HR_LNG_imp</t>
         </is>
       </c>
       <c r="C146" t="n">
@@ -38873,7 +38879,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>AS_LNG_exp</t>
+          <t>EE_LNG_imp</t>
         </is>
       </c>
       <c r="C147" t="n">
@@ -38888,7 +38894,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>RU_LNG_exp</t>
+          <t>FI_LNG_imp</t>
         </is>
       </c>
       <c r="C148" t="n">
@@ -38903,7 +38909,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>EG_LNG_exp</t>
+          <t>FR_LNG_imp</t>
         </is>
       </c>
       <c r="C149" t="n">
@@ -38918,7 +38924,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>IM_LNG_exp</t>
+          <t>DE_LNG_imp</t>
         </is>
       </c>
       <c r="C150" t="n">
@@ -38933,7 +38939,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>BE_LNG_imp</t>
+          <t>EL_LNG_imp</t>
         </is>
       </c>
       <c r="C151" t="n">
@@ -38948,7 +38954,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>HR_LNG_imp</t>
+          <t>IE_LNG_imp</t>
         </is>
       </c>
       <c r="C152" t="n">
@@ -38963,7 +38969,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>EE_LNG_imp</t>
+          <t>IT_LNG_imp</t>
         </is>
       </c>
       <c r="C153" t="n">
@@ -38978,7 +38984,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>FI_LNG_imp</t>
+          <t>LV_LNG_imp</t>
         </is>
       </c>
       <c r="C154" t="n">
@@ -38993,7 +38999,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>FR_LNG_imp</t>
+          <t>LT_LNG_imp</t>
         </is>
       </c>
       <c r="C155" t="n">
@@ -39008,7 +39014,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>DE_LNG_imp</t>
+          <t>NL_LNG_imp</t>
         </is>
       </c>
       <c r="C156" t="n">
@@ -39023,7 +39029,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>EL_LNG_imp</t>
+          <t>PL_LNG_imp</t>
         </is>
       </c>
       <c r="C157" t="n">
@@ -39038,7 +39044,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>IE_LNG_imp</t>
+          <t>PT_LNG_imp</t>
         </is>
       </c>
       <c r="C158" t="n">
@@ -39053,7 +39059,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>IT_LNG_imp</t>
+          <t>ES_LNG_imp</t>
         </is>
       </c>
       <c r="C159" t="n">
@@ -39068,7 +39074,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>LV_LNG_imp</t>
+          <t>TR_LNG_imp</t>
         </is>
       </c>
       <c r="C160" t="n">
@@ -39083,7 +39089,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>LT_LNG_imp</t>
+          <t>UK_LNG_imp</t>
         </is>
       </c>
       <c r="C161" t="n">
@@ -39098,7 +39104,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>NL_LNG_imp</t>
+          <t>USA_LNG_imp</t>
         </is>
       </c>
       <c r="C162" t="n">
@@ -39113,7 +39119,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>PL_LNG_imp</t>
+          <t>SA_LNG_imp</t>
         </is>
       </c>
       <c r="C163" t="n">
@@ -39128,7 +39134,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>PT_LNG_imp</t>
+          <t>TT_LNG_imp</t>
         </is>
       </c>
       <c r="C164" t="n">
@@ -39143,7 +39149,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>ES_LNG_imp</t>
+          <t>ME_LNG_imp</t>
         </is>
       </c>
       <c r="C165" t="n">
@@ -39158,7 +39164,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>TR_LNG_imp</t>
+          <t>QA_LNG_imp</t>
         </is>
       </c>
       <c r="C166" t="n">
@@ -39173,7 +39179,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>UK_LNG_imp</t>
+          <t>AF_LNG_imp</t>
         </is>
       </c>
       <c r="C167" t="n">
@@ -39188,7 +39194,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>USA_LNG_imp</t>
+          <t>AU_LNG_imp</t>
         </is>
       </c>
       <c r="C168" t="n">
@@ -39203,7 +39209,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>SA_LNG_imp</t>
+          <t>CN_LNG_imp</t>
         </is>
       </c>
       <c r="C169" t="n">
@@ -39218,7 +39224,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>TT_LNG_imp</t>
+          <t>JS_LNG_imp</t>
         </is>
       </c>
       <c r="C170" t="n">
@@ -39233,7 +39239,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>ME_LNG_imp</t>
+          <t>IN_LNG_imp</t>
         </is>
       </c>
       <c r="C171" t="n">
@@ -39248,7 +39254,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>QA_LNG_imp</t>
+          <t>AS_LNG_imp</t>
         </is>
       </c>
       <c r="C172" t="n">
@@ -39263,7 +39269,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>AF_LNG_imp</t>
+          <t>RU_LNG_imp</t>
         </is>
       </c>
       <c r="C173" t="n">
@@ -39278,7 +39284,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>AU_LNG_imp</t>
+          <t>EG_LNG_imp</t>
         </is>
       </c>
       <c r="C174" t="n">
@@ -39293,7 +39299,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>CN_LNG_imp</t>
+          <t>IM_LNG_imp</t>
         </is>
       </c>
       <c r="C175" t="n">
@@ -39303,12 +39309,12 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Methane</t>
+          <t>Hydrogen</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>JS_LNG_imp</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="C176" t="n">
@@ -39318,12 +39324,12 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Methane</t>
+          <t>Hydrogen</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>IN_LNG_imp</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="C177" t="n">
@@ -39333,12 +39339,12 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Methane</t>
+          <t>Hydrogen</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>AS_LNG_imp</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="C178" t="n">
@@ -39348,12 +39354,12 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Methane</t>
+          <t>Hydrogen</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>RU_LNG_imp</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="C179" t="n">
@@ -39363,12 +39369,12 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Methane</t>
+          <t>Hydrogen</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>EG_LNG_imp</t>
+          <t>BG</t>
         </is>
       </c>
       <c r="C180" t="n">
@@ -39378,12 +39384,12 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Methane</t>
+          <t>Hydrogen</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>IM_LNG_imp</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="C181" t="n">
@@ -39398,7 +39404,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>CZ</t>
         </is>
       </c>
       <c r="C182" t="n">
@@ -39413,7 +39419,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>AT</t>
+          <t>DK</t>
         </is>
       </c>
       <c r="C183" t="n">
@@ -39428,7 +39434,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>BE</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="C184" t="n">
@@ -39443,7 +39449,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="C185" t="n">
@@ -39458,7 +39464,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>BG</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="C186" t="n">
@@ -39473,7 +39479,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="C187" t="n">
@@ -39488,7 +39494,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>CZ</t>
+          <t>EL</t>
         </is>
       </c>
       <c r="C188" t="n">
@@ -39503,7 +39509,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>DK</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="C189" t="n">
@@ -39518,7 +39524,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>EE</t>
+          <t>IE</t>
         </is>
       </c>
       <c r="C190" t="n">
@@ -39533,7 +39539,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="C191" t="n">
@@ -39548,7 +39554,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>LV</t>
         </is>
       </c>
       <c r="C192" t="n">
@@ -39563,7 +39569,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>LT</t>
         </is>
       </c>
       <c r="C193" t="n">
@@ -39578,7 +39584,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>EL</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="C194" t="n">
@@ -39593,7 +39599,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>HU</t>
+          <t>MD</t>
         </is>
       </c>
       <c r="C195" t="n">
@@ -39608,7 +39614,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>IE</t>
+          <t>NL</t>
         </is>
       </c>
       <c r="C196" t="n">
@@ -39623,7 +39629,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>MK</t>
         </is>
       </c>
       <c r="C197" t="n">
@@ -39638,7 +39644,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>LV</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="C198" t="n">
@@ -39653,7 +39659,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>LT</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="C199" t="n">
@@ -39668,7 +39674,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>LU</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="C200" t="n">
@@ -39683,7 +39689,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>MD</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="C201" t="n">
@@ -39698,7 +39704,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>NL</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="C202" t="n">
@@ -39713,7 +39719,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>MK</t>
+          <t>SK</t>
         </is>
       </c>
       <c r="C203" t="n">
@@ -39728,7 +39734,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="C204" t="n">
@@ -39743,7 +39749,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C205" t="n">
@@ -39758,7 +39764,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="C206" t="n">
@@ -39773,7 +39779,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>RO</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="C207" t="n">
@@ -39788,7 +39794,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>TR</t>
         </is>
       </c>
       <c r="C208" t="n">
@@ -39803,7 +39809,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>SK</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="C209" t="n">
@@ -39818,7 +39824,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>UA</t>
         </is>
       </c>
       <c r="C210" t="n">
@@ -39833,7 +39839,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>AL_Prod</t>
         </is>
       </c>
       <c r="C211" t="n">
@@ -39848,7 +39854,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>DZ_Prod</t>
         </is>
       </c>
       <c r="C212" t="n">
@@ -39863,7 +39869,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>AT_Prod</t>
         </is>
       </c>
       <c r="C213" t="n">
@@ -39878,7 +39884,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>TR</t>
+          <t>BY_Prod</t>
         </is>
       </c>
       <c r="C214" t="n">
@@ -39893,7 +39899,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>BE_Prod</t>
         </is>
       </c>
       <c r="C215" t="n">
@@ -39908,7 +39914,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>UA</t>
+          <t>BA_Prod</t>
         </is>
       </c>
       <c r="C216" t="n">
@@ -39923,7 +39929,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>AL_Prod</t>
+          <t>BG_Prod</t>
         </is>
       </c>
       <c r="C217" t="n">
@@ -39938,7 +39944,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>DZ_Prod</t>
+          <t>HR_Prod</t>
         </is>
       </c>
       <c r="C218" t="n">
@@ -39953,7 +39959,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>AT_Prod</t>
+          <t>CZ_Prod</t>
         </is>
       </c>
       <c r="C219" t="n">
@@ -39968,7 +39974,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>BY_Prod</t>
+          <t>DK_Prod</t>
         </is>
       </c>
       <c r="C220" t="n">
@@ -39983,7 +39989,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>BE_Prod</t>
+          <t>EE_Prod</t>
         </is>
       </c>
       <c r="C221" t="n">
@@ -39998,7 +40004,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>BA_Prod</t>
+          <t>FI_Prod</t>
         </is>
       </c>
       <c r="C222" t="n">
@@ -40013,7 +40019,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>BG_Prod</t>
+          <t>FR_Prod</t>
         </is>
       </c>
       <c r="C223" t="n">
@@ -40028,7 +40034,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>HR_Prod</t>
+          <t>DE_Prod</t>
         </is>
       </c>
       <c r="C224" t="n">
@@ -40043,7 +40049,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>CZ_Prod</t>
+          <t>EL_Prod</t>
         </is>
       </c>
       <c r="C225" t="n">
@@ -40058,7 +40064,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>DK_Prod</t>
+          <t>HU_Prod</t>
         </is>
       </c>
       <c r="C226" t="n">
@@ -40073,7 +40079,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>EE_Prod</t>
+          <t>IE_Prod</t>
         </is>
       </c>
       <c r="C227" t="n">
@@ -40088,7 +40094,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>FI_Prod</t>
+          <t>IT_Prod</t>
         </is>
       </c>
       <c r="C228" t="n">
@@ -40103,7 +40109,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>FR_Prod</t>
+          <t>LV_Prod</t>
         </is>
       </c>
       <c r="C229" t="n">
@@ -40118,7 +40124,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>DE_Prod</t>
+          <t>LY_Prod</t>
         </is>
       </c>
       <c r="C230" t="n">
@@ -40133,7 +40139,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>EL_Prod</t>
+          <t>LT_Prod</t>
         </is>
       </c>
       <c r="C231" t="n">
@@ -40148,7 +40154,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>HU_Prod</t>
+          <t>LU_Prod</t>
         </is>
       </c>
       <c r="C232" t="n">
@@ -40163,7 +40169,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>IE_Prod</t>
+          <t>MD_Prod</t>
         </is>
       </c>
       <c r="C233" t="n">
@@ -40178,7 +40184,7 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>IT_Prod</t>
+          <t>NL_Prod</t>
         </is>
       </c>
       <c r="C234" t="n">
@@ -40193,7 +40199,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>LV_Prod</t>
+          <t>MK_Prod</t>
         </is>
       </c>
       <c r="C235" t="n">
@@ -40208,7 +40214,7 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>LY_Prod</t>
+          <t>NO_Prod</t>
         </is>
       </c>
       <c r="C236" t="n">
@@ -40223,7 +40229,7 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>LT_Prod</t>
+          <t>PL_Prod</t>
         </is>
       </c>
       <c r="C237" t="n">
@@ -40238,7 +40244,7 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>LU_Prod</t>
+          <t>PT_Prod</t>
         </is>
       </c>
       <c r="C238" t="n">
@@ -40253,7 +40259,7 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>MD_Prod</t>
+          <t>RO_Prod</t>
         </is>
       </c>
       <c r="C239" t="n">
@@ -40268,7 +40274,7 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>NL_Prod</t>
+          <t>RU_Prod</t>
         </is>
       </c>
       <c r="C240" t="n">
@@ -40283,7 +40289,7 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>MK_Prod</t>
+          <t>RS_Prod</t>
         </is>
       </c>
       <c r="C241" t="n">
@@ -40298,7 +40304,7 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>NO_Prod</t>
+          <t>SK_Prod</t>
         </is>
       </c>
       <c r="C242" t="n">
@@ -40313,7 +40319,7 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>PL_Prod</t>
+          <t>SI_Prod</t>
         </is>
       </c>
       <c r="C243" t="n">
@@ -40328,7 +40334,7 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>PT_Prod</t>
+          <t>CH_Prod</t>
         </is>
       </c>
       <c r="C244" t="n">
@@ -40343,7 +40349,7 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>RO_Prod</t>
+          <t>TN_Prod</t>
         </is>
       </c>
       <c r="C245" t="n">
@@ -40358,7 +40364,7 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>RU_Prod</t>
+          <t>TR_Prod</t>
         </is>
       </c>
       <c r="C246" t="n">
@@ -40373,7 +40379,7 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>RS_Prod</t>
+          <t>UK_Prod</t>
         </is>
       </c>
       <c r="C247" t="n">
@@ -40388,7 +40394,7 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>SK_Prod</t>
+          <t>UA_Prod</t>
         </is>
       </c>
       <c r="C248" t="n">
@@ -40403,7 +40409,7 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>SI_Prod</t>
+          <t>ES_Prod</t>
         </is>
       </c>
       <c r="C249" t="n">
@@ -40418,7 +40424,7 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>CH_Prod</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="C250" t="n">
@@ -40433,7 +40439,7 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>TN_Prod</t>
+          <t>CM</t>
         </is>
       </c>
       <c r="C251" t="n">
@@ -40448,7 +40454,7 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>TR_Prod</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="C252" t="n">
@@ -40463,7 +40469,7 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>UK_Prod</t>
+          <t>TT</t>
         </is>
       </c>
       <c r="C253" t="n">
@@ -40478,7 +40484,7 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>UA_Prod</t>
+          <t>ME</t>
         </is>
       </c>
       <c r="C254" t="n">
@@ -40493,7 +40499,7 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>ES_Prod</t>
+          <t>QA</t>
         </is>
       </c>
       <c r="C255" t="n">
@@ -40508,7 +40514,7 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>AF</t>
         </is>
       </c>
       <c r="C256" t="n">
@@ -40523,7 +40529,7 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>CM</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="C257" t="n">
@@ -40538,7 +40544,7 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="C258" t="n">
@@ -40553,7 +40559,7 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>TT</t>
+          <t>JS</t>
         </is>
       </c>
       <c r="C259" t="n">
@@ -40568,7 +40574,7 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>ME</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="C260" t="n">
@@ -40583,7 +40589,7 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>QA</t>
+          <t>AS</t>
         </is>
       </c>
       <c r="C261" t="n">
@@ -40598,7 +40604,7 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>AF</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="C262" t="n">
@@ -40613,7 +40619,7 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>RU</t>
         </is>
       </c>
       <c r="C263" t="n">
@@ -40628,7 +40634,7 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>DZ</t>
         </is>
       </c>
       <c r="C264" t="n">
@@ -40643,7 +40649,7 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>JS</t>
+          <t>LY</t>
         </is>
       </c>
       <c r="C265" t="n">
@@ -40658,7 +40664,7 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>TN</t>
         </is>
       </c>
       <c r="C266" t="n">
@@ -40673,7 +40679,7 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>AS</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="C267" t="n">
@@ -40688,7 +40694,7 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="C268" t="n">
@@ -40703,7 +40709,7 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>RU</t>
+          <t>IM</t>
         </is>
       </c>
       <c r="C269" t="n">
@@ -40718,7 +40724,7 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>DZ</t>
+          <t>BY</t>
         </is>
       </c>
       <c r="C270" t="n">
@@ -40733,7 +40739,7 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>LY</t>
+          <t>USA_Prod</t>
         </is>
       </c>
       <c r="C271" t="n">
@@ -40748,7 +40754,7 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>TN</t>
+          <t>CM_Prod</t>
         </is>
       </c>
       <c r="C272" t="n">
@@ -40763,7 +40769,7 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>SA_Prod</t>
         </is>
       </c>
       <c r="C273" t="n">
@@ -40778,7 +40784,7 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>TT_Prod</t>
         </is>
       </c>
       <c r="C274" t="n">
@@ -40793,7 +40799,7 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>IM</t>
+          <t>ME_Prod</t>
         </is>
       </c>
       <c r="C275" t="n">
@@ -40808,7 +40814,7 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>BY</t>
+          <t>QA_Prod</t>
         </is>
       </c>
       <c r="C276" t="n">
@@ -40823,7 +40829,7 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>AF_Prod</t>
         </is>
       </c>
       <c r="C277" t="n">
@@ -40838,7 +40844,7 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Tunisia</t>
+          <t>MA_Prod</t>
         </is>
       </c>
       <c r="C278" t="n">
@@ -40853,7 +40859,7 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Libya</t>
+          <t>AU_Prod</t>
         </is>
       </c>
       <c r="C279" t="n">
@@ -40868,7 +40874,7 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>USA_Prod</t>
+          <t>CN_Prod</t>
         </is>
       </c>
       <c r="C280" t="n">
@@ -40883,7 +40889,7 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>CM_Prod</t>
+          <t>JS_Prod</t>
         </is>
       </c>
       <c r="C281" t="n">
@@ -40898,7 +40904,7 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>SA_Prod</t>
+          <t>IN_Prod</t>
         </is>
       </c>
       <c r="C282" t="n">
@@ -40913,7 +40919,7 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>TT_Prod</t>
+          <t>AS_Prod</t>
         </is>
       </c>
       <c r="C283" t="n">
@@ -40928,7 +40934,7 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>ME_Prod</t>
+          <t>CR_Prod</t>
         </is>
       </c>
       <c r="C284" t="n">
@@ -40943,7 +40949,7 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>QA_Prod</t>
+          <t>EG_Prod</t>
         </is>
       </c>
       <c r="C285" t="n">
@@ -40958,7 +40964,7 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>AF_Prod</t>
+          <t>IM_Prod</t>
         </is>
       </c>
       <c r="C286" t="n">
@@ -40973,7 +40979,7 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>MA_Prod</t>
+          <t>SE_Prod</t>
         </is>
       </c>
       <c r="C287" t="n">
@@ -40988,7 +40994,7 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>AU_Prod</t>
+          <t>BE_LNG_exp</t>
         </is>
       </c>
       <c r="C288" t="n">
@@ -41003,7 +41009,7 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>CN_Prod</t>
+          <t>HR_LNG_exp</t>
         </is>
       </c>
       <c r="C289" t="n">
@@ -41018,7 +41024,7 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>JS_Prod</t>
+          <t>EE_LNG_exp</t>
         </is>
       </c>
       <c r="C290" t="n">
@@ -41033,7 +41039,7 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>IN_Prod</t>
+          <t>FI_LNG_exp</t>
         </is>
       </c>
       <c r="C291" t="n">
@@ -41048,7 +41054,7 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>AS_Prod</t>
+          <t>FR_LNG_exp</t>
         </is>
       </c>
       <c r="C292" t="n">
@@ -41063,7 +41069,7 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>CR_Prod</t>
+          <t>DE_LNG_exp</t>
         </is>
       </c>
       <c r="C293" t="n">
@@ -41078,7 +41084,7 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>EG_Prod</t>
+          <t>EL_LNG_exp</t>
         </is>
       </c>
       <c r="C294" t="n">
@@ -41093,7 +41099,7 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>IM_Prod</t>
+          <t>IE_LNG_exp</t>
         </is>
       </c>
       <c r="C295" t="n">
@@ -41108,7 +41114,7 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>SE_Prod</t>
+          <t>IT_LNG_exp</t>
         </is>
       </c>
       <c r="C296" t="n">
@@ -41123,7 +41129,7 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>nan_Prod</t>
+          <t>LV_LNG_exp</t>
         </is>
       </c>
       <c r="C297" t="n">
@@ -41138,7 +41144,7 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>Tunisia_Prod</t>
+          <t>LT_LNG_exp</t>
         </is>
       </c>
       <c r="C298" t="n">
@@ -41153,7 +41159,7 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>Libya_Prod</t>
+          <t>NL_LNG_exp</t>
         </is>
       </c>
       <c r="C299" t="n">
@@ -41168,7 +41174,7 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>BE_LNG_exp</t>
+          <t>PL_LNG_exp</t>
         </is>
       </c>
       <c r="C300" t="n">
@@ -41183,7 +41189,7 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>HR_LNG_exp</t>
+          <t>PT_LNG_exp</t>
         </is>
       </c>
       <c r="C301" t="n">
@@ -41198,7 +41204,7 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>EE_LNG_exp</t>
+          <t>ES_LNG_exp</t>
         </is>
       </c>
       <c r="C302" t="n">
@@ -41213,7 +41219,7 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>FI_LNG_exp</t>
+          <t>TR_LNG_exp</t>
         </is>
       </c>
       <c r="C303" t="n">
@@ -41228,7 +41234,7 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>FR_LNG_exp</t>
+          <t>UK_LNG_exp</t>
         </is>
       </c>
       <c r="C304" t="n">
@@ -41243,7 +41249,7 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>DE_LNG_exp</t>
+          <t>USA_LNG_exp</t>
         </is>
       </c>
       <c r="C305" t="n">
@@ -41258,7 +41264,7 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>EL_LNG_exp</t>
+          <t>SA_LNG_exp</t>
         </is>
       </c>
       <c r="C306" t="n">
@@ -41273,7 +41279,7 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>IE_LNG_exp</t>
+          <t>TT_LNG_exp</t>
         </is>
       </c>
       <c r="C307" t="n">
@@ -41288,7 +41294,7 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>IT_LNG_exp</t>
+          <t>ME_LNG_exp</t>
         </is>
       </c>
       <c r="C308" t="n">
@@ -41303,7 +41309,7 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>LV_LNG_exp</t>
+          <t>QA_LNG_exp</t>
         </is>
       </c>
       <c r="C309" t="n">
@@ -41318,7 +41324,7 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>LT_LNG_exp</t>
+          <t>AF_LNG_exp</t>
         </is>
       </c>
       <c r="C310" t="n">
@@ -41333,7 +41339,7 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>NL_LNG_exp</t>
+          <t>AU_LNG_exp</t>
         </is>
       </c>
       <c r="C311" t="n">
@@ -41348,7 +41354,7 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>PL_LNG_exp</t>
+          <t>CN_LNG_exp</t>
         </is>
       </c>
       <c r="C312" t="n">
@@ -41363,7 +41369,7 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>PT_LNG_exp</t>
+          <t>JS_LNG_exp</t>
         </is>
       </c>
       <c r="C313" t="n">
@@ -41378,7 +41384,7 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>ES_LNG_exp</t>
+          <t>IN_LNG_exp</t>
         </is>
       </c>
       <c r="C314" t="n">
@@ -41393,7 +41399,7 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>TR_LNG_exp</t>
+          <t>AS_LNG_exp</t>
         </is>
       </c>
       <c r="C315" t="n">
@@ -41408,7 +41414,7 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>UK_LNG_exp</t>
+          <t>RU_LNG_exp</t>
         </is>
       </c>
       <c r="C316" t="n">
@@ -41423,7 +41429,7 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>USA_LNG_exp</t>
+          <t>EG_LNG_exp</t>
         </is>
       </c>
       <c r="C317" t="n">
@@ -41438,7 +41444,7 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>SA_LNG_exp</t>
+          <t>IM_LNG_exp</t>
         </is>
       </c>
       <c r="C318" t="n">
@@ -41453,7 +41459,7 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>TT_LNG_exp</t>
+          <t>BE_LNG_imp</t>
         </is>
       </c>
       <c r="C319" t="n">
@@ -41468,7 +41474,7 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>ME_LNG_exp</t>
+          <t>HR_LNG_imp</t>
         </is>
       </c>
       <c r="C320" t="n">
@@ -41483,7 +41489,7 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>QA_LNG_exp</t>
+          <t>EE_LNG_imp</t>
         </is>
       </c>
       <c r="C321" t="n">
@@ -41498,7 +41504,7 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>AF_LNG_exp</t>
+          <t>FI_LNG_imp</t>
         </is>
       </c>
       <c r="C322" t="n">
@@ -41513,7 +41519,7 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>AU_LNG_exp</t>
+          <t>FR_LNG_imp</t>
         </is>
       </c>
       <c r="C323" t="n">
@@ -41528,7 +41534,7 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>CN_LNG_exp</t>
+          <t>DE_LNG_imp</t>
         </is>
       </c>
       <c r="C324" t="n">
@@ -41543,7 +41549,7 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>JS_LNG_exp</t>
+          <t>EL_LNG_imp</t>
         </is>
       </c>
       <c r="C325" t="n">
@@ -41558,7 +41564,7 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>IN_LNG_exp</t>
+          <t>IE_LNG_imp</t>
         </is>
       </c>
       <c r="C326" t="n">
@@ -41573,7 +41579,7 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>AS_LNG_exp</t>
+          <t>IT_LNG_imp</t>
         </is>
       </c>
       <c r="C327" t="n">
@@ -41588,7 +41594,7 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>RU_LNG_exp</t>
+          <t>LV_LNG_imp</t>
         </is>
       </c>
       <c r="C328" t="n">
@@ -41603,7 +41609,7 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>EG_LNG_exp</t>
+          <t>LT_LNG_imp</t>
         </is>
       </c>
       <c r="C329" t="n">
@@ -41618,7 +41624,7 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>IM_LNG_exp</t>
+          <t>NL_LNG_imp</t>
         </is>
       </c>
       <c r="C330" t="n">
@@ -41633,7 +41639,7 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>BE_LNG_imp</t>
+          <t>PL_LNG_imp</t>
         </is>
       </c>
       <c r="C331" t="n">
@@ -41648,7 +41654,7 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>HR_LNG_imp</t>
+          <t>PT_LNG_imp</t>
         </is>
       </c>
       <c r="C332" t="n">
@@ -41663,7 +41669,7 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>EE_LNG_imp</t>
+          <t>ES_LNG_imp</t>
         </is>
       </c>
       <c r="C333" t="n">
@@ -41678,7 +41684,7 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>FI_LNG_imp</t>
+          <t>TR_LNG_imp</t>
         </is>
       </c>
       <c r="C334" t="n">
@@ -41693,7 +41699,7 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>FR_LNG_imp</t>
+          <t>UK_LNG_imp</t>
         </is>
       </c>
       <c r="C335" t="n">
@@ -41708,7 +41714,7 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>DE_LNG_imp</t>
+          <t>USA_LNG_imp</t>
         </is>
       </c>
       <c r="C336" t="n">
@@ -41723,7 +41729,7 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>EL_LNG_imp</t>
+          <t>SA_LNG_imp</t>
         </is>
       </c>
       <c r="C337" t="n">
@@ -41738,7 +41744,7 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>IE_LNG_imp</t>
+          <t>TT_LNG_imp</t>
         </is>
       </c>
       <c r="C338" t="n">
@@ -41753,7 +41759,7 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>IT_LNG_imp</t>
+          <t>ME_LNG_imp</t>
         </is>
       </c>
       <c r="C339" t="n">
@@ -41768,7 +41774,7 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>LV_LNG_imp</t>
+          <t>QA_LNG_imp</t>
         </is>
       </c>
       <c r="C340" t="n">
@@ -41783,7 +41789,7 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>LT_LNG_imp</t>
+          <t>AF_LNG_imp</t>
         </is>
       </c>
       <c r="C341" t="n">
@@ -41798,7 +41804,7 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>NL_LNG_imp</t>
+          <t>AU_LNG_imp</t>
         </is>
       </c>
       <c r="C342" t="n">
@@ -41813,7 +41819,7 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>PL_LNG_imp</t>
+          <t>CN_LNG_imp</t>
         </is>
       </c>
       <c r="C343" t="n">
@@ -41828,7 +41834,7 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>PT_LNG_imp</t>
+          <t>JS_LNG_imp</t>
         </is>
       </c>
       <c r="C344" t="n">
@@ -41843,7 +41849,7 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>ES_LNG_imp</t>
+          <t>IN_LNG_imp</t>
         </is>
       </c>
       <c r="C345" t="n">
@@ -41858,7 +41864,7 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>TR_LNG_imp</t>
+          <t>AS_LNG_imp</t>
         </is>
       </c>
       <c r="C346" t="n">
@@ -41873,7 +41879,7 @@
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>UK_LNG_imp</t>
+          <t>RU_LNG_imp</t>
         </is>
       </c>
       <c r="C347" t="n">
@@ -41888,7 +41894,7 @@
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>USA_LNG_imp</t>
+          <t>EG_LNG_imp</t>
         </is>
       </c>
       <c r="C348" t="n">
@@ -41903,190 +41909,10 @@
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>SA_LNG_imp</t>
+          <t>IM_LNG_imp</t>
         </is>
       </c>
       <c r="C349" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="350">
-      <c r="A350" t="inlineStr">
-        <is>
-          <t>Hydrogen</t>
-        </is>
-      </c>
-      <c r="B350" t="inlineStr">
-        <is>
-          <t>TT_LNG_imp</t>
-        </is>
-      </c>
-      <c r="C350" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="351">
-      <c r="A351" t="inlineStr">
-        <is>
-          <t>Hydrogen</t>
-        </is>
-      </c>
-      <c r="B351" t="inlineStr">
-        <is>
-          <t>ME_LNG_imp</t>
-        </is>
-      </c>
-      <c r="C351" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="352">
-      <c r="A352" t="inlineStr">
-        <is>
-          <t>Hydrogen</t>
-        </is>
-      </c>
-      <c r="B352" t="inlineStr">
-        <is>
-          <t>QA_LNG_imp</t>
-        </is>
-      </c>
-      <c r="C352" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="353">
-      <c r="A353" t="inlineStr">
-        <is>
-          <t>Hydrogen</t>
-        </is>
-      </c>
-      <c r="B353" t="inlineStr">
-        <is>
-          <t>AF_LNG_imp</t>
-        </is>
-      </c>
-      <c r="C353" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="354">
-      <c r="A354" t="inlineStr">
-        <is>
-          <t>Hydrogen</t>
-        </is>
-      </c>
-      <c r="B354" t="inlineStr">
-        <is>
-          <t>AU_LNG_imp</t>
-        </is>
-      </c>
-      <c r="C354" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="355">
-      <c r="A355" t="inlineStr">
-        <is>
-          <t>Hydrogen</t>
-        </is>
-      </c>
-      <c r="B355" t="inlineStr">
-        <is>
-          <t>CN_LNG_imp</t>
-        </is>
-      </c>
-      <c r="C355" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="356">
-      <c r="A356" t="inlineStr">
-        <is>
-          <t>Hydrogen</t>
-        </is>
-      </c>
-      <c r="B356" t="inlineStr">
-        <is>
-          <t>JS_LNG_imp</t>
-        </is>
-      </c>
-      <c r="C356" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="357">
-      <c r="A357" t="inlineStr">
-        <is>
-          <t>Hydrogen</t>
-        </is>
-      </c>
-      <c r="B357" t="inlineStr">
-        <is>
-          <t>IN_LNG_imp</t>
-        </is>
-      </c>
-      <c r="C357" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="358">
-      <c r="A358" t="inlineStr">
-        <is>
-          <t>Hydrogen</t>
-        </is>
-      </c>
-      <c r="B358" t="inlineStr">
-        <is>
-          <t>AS_LNG_imp</t>
-        </is>
-      </c>
-      <c r="C358" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="359">
-      <c r="A359" t="inlineStr">
-        <is>
-          <t>Hydrogen</t>
-        </is>
-      </c>
-      <c r="B359" t="inlineStr">
-        <is>
-          <t>RU_LNG_imp</t>
-        </is>
-      </c>
-      <c r="C359" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="360">
-      <c r="A360" t="inlineStr">
-        <is>
-          <t>Hydrogen</t>
-        </is>
-      </c>
-      <c r="B360" t="inlineStr">
-        <is>
-          <t>EG_LNG_imp</t>
-        </is>
-      </c>
-      <c r="C360" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="361">
-      <c r="A361" t="inlineStr">
-        <is>
-          <t>Hydrogen</t>
-        </is>
-      </c>
-      <c r="B361" t="inlineStr">
-        <is>
-          <t>IM_LNG_imp</t>
-        </is>
-      </c>
-      <c r="C361" t="n">
         <v>0</v>
       </c>
     </row>
